--- a/fixtures/xlsx/basic/input.xlsx
+++ b/fixtures/xlsx/basic/input.xlsx
@@ -8,15 +8,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Alice</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t>42</t>
+    <t>Alice</t>
   </si>
   <si>
     <t>Name</t>
@@ -29,18 +26,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/xlsx/basic/input.xlsx
+++ b/fixtures/xlsx/basic/input.xlsx
@@ -10,13 +10,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>Value</t>
   </si>
   <si>
     <t>Alice</t>
-  </si>
-  <si>
-    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -26,15 +26,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>42</v>

--- a/fixtures/xlsx/basic/input.xlsx
+++ b/fixtures/xlsx/basic/input.xlsx
@@ -10,13 +10,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
     <t>Alice</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -26,15 +26,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>42</v>
